--- a/library/04_Arknights_Endfield.xlsx
+++ b/library/04_Arknights_Endfield.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wuthering Waves" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wuthering Waves'!$A$1:$D$1</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -407,47 +405,4 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Имя персонажа</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Стихия</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Редкость</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>